--- a/Outputs/Recycling_Plot_Data/ACCII/03_National_Timeseries_data_ACCII.xlsx
+++ b/Outputs/Recycling_Plot_Data/ACCII/03_National_Timeseries_data_ACCII.xlsx
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1.409839815604137</v>
+        <v>1.234041159603472</v>
       </c>
     </row>
     <row r="3">
@@ -424,7 +424,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1.331674803857383</v>
+        <v>1.165827772808572</v>
       </c>
     </row>
     <row r="4">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>0.8487528357655363</v>
+        <v>0.7403889381360347</v>
       </c>
     </row>
     <row r="7">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>0.8014864492384076</v>
+        <v>0.6992568241458127</v>
       </c>
     </row>
     <row r="8">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>1.775352014052066</v>
+        <v>1.775240294417501</v>
       </c>
     </row>
     <row r="13">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E13">
-        <v>1.589439005173939</v>
+        <v>1.589339375059251</v>
       </c>
     </row>
     <row r="14">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="E16">
-        <v>1.073770106228046</v>
+        <v>1.073700961883469</v>
       </c>
     </row>
     <row r="17">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="E17">
-        <v>0.960885192006819</v>
+        <v>0.9608235299810965</v>
       </c>
     </row>
     <row r="18">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="E18">
-        <v>0.008964279684668914</v>
+        <v>0.008846934702659986</v>
       </c>
     </row>
     <row r="19">
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="E19">
-        <v>0.008856711103025139</v>
+        <v>0.008742904047828863</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="E22">
-        <v>2.309124171017272</v>
+        <v>2.30893713617657</v>
       </c>
     </row>
     <row r="23">
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="E23">
-        <v>1.960982969526287</v>
+        <v>1.960824909740873</v>
       </c>
     </row>
     <row r="24">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="E28">
-        <v>0.01846788305604798</v>
+        <v>0.01828576635881121</v>
       </c>
     </row>
     <row r="29">
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="E29">
-        <v>0.01792794386291564</v>
+        <v>0.01775130591855304</v>
       </c>
     </row>
     <row r="30">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="E32">
-        <v>2.99354292018189</v>
+        <v>2.993224376927201</v>
       </c>
     </row>
     <row r="33">
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="E33">
-        <v>2.415289787048803</v>
+        <v>2.415034405861705</v>
       </c>
     </row>
     <row r="34">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="E36">
-        <v>1.826261478220285</v>
+        <v>1.826062439727264</v>
       </c>
     </row>
     <row r="37">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="E38">
-        <v>0.03273386863556026</v>
+        <v>0.03244565680461085</v>
       </c>
     </row>
     <row r="39">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E39">
-        <v>0.03132015085827669</v>
+        <v>0.03104064461982902</v>
       </c>
     </row>
     <row r="40">
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="E42">
-        <v>3.657136246505403</v>
+        <v>3.656604184702757</v>
       </c>
     </row>
     <row r="43">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="E43">
-        <v>2.807619312188081</v>
+        <v>2.807213637188688</v>
       </c>
     </row>
     <row r="44">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="E48">
-        <v>0.05437943538347214</v>
+        <v>0.05392920285611788</v>
       </c>
     </row>
     <row r="49">
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="E49">
-        <v>0.05129648834844233</v>
+        <v>0.05085986741102698</v>
       </c>
     </row>
     <row r="50">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="E52">
-        <v>4.456195136359008</v>
+        <v>4.455302441395641</v>
       </c>
     </row>
     <row r="53">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="E53">
-        <v>3.259866852727868</v>
+        <v>3.259219096977254</v>
       </c>
     </row>
     <row r="54">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="E56">
-        <v>2.731760085557775</v>
+        <v>2.731198755822515</v>
       </c>
     </row>
     <row r="57">
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="E58">
-        <v>0.08588360943122554</v>
+        <v>0.08517625082816997</v>
       </c>
     </row>
     <row r="59">
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="E59">
-        <v>0.07984513540702765</v>
+        <v>0.07915894016570797</v>
       </c>
     </row>
     <row r="60">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="E62">
-        <v>5.219266487522941</v>
+        <v>5.217784556063381</v>
       </c>
     </row>
     <row r="63">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="E63">
-        <v>3.645312932159311</v>
+        <v>3.644287117788819</v>
       </c>
     </row>
     <row r="64">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="E66">
-        <v>3.196194908055735</v>
+        <v>3.195262252827635</v>
       </c>
     </row>
     <row r="67">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="E68">
-        <v>0.1323817639014069</v>
+        <v>0.1312809386604273</v>
       </c>
     </row>
     <row r="69">
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="E69">
-        <v>0.1215194287220713</v>
+        <v>0.1204512457447614</v>
       </c>
     </row>
     <row r="70">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="E72">
-        <v>6.007269654937696</v>
+        <v>6.004842218153445</v>
       </c>
     </row>
     <row r="73">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E73">
-        <v>4.007490319729238</v>
+        <v>4.005886521514782</v>
       </c>
     </row>
     <row r="74">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="E74">
-        <v>5.828813530892933</v>
+        <v>5.826391627515035</v>
       </c>
     </row>
     <row r="75">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E76">
-        <v>3.679732009095141</v>
+        <v>3.678203060650428</v>
       </c>
     </row>
     <row r="77">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="E78">
-        <v>0.1935103049529375</v>
+        <v>0.1918000631025382</v>
       </c>
     </row>
     <row r="79">
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="E79">
-        <v>0.1750948051911595</v>
+        <v>0.1734354883721286</v>
       </c>
     </row>
     <row r="80">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="E82">
-        <v>7.018621920087188</v>
+        <v>7.014721440285064</v>
       </c>
     </row>
     <row r="83">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="E83">
-        <v>4.476358261273396</v>
+        <v>4.473899846988985</v>
       </c>
     </row>
     <row r="84">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="E84">
-        <v>6.815858032945934</v>
+        <v>6.811960723041302</v>
       </c>
     </row>
     <row r="85">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="E86">
-        <v>4.302853546498211</v>
+        <v>4.300393173400079</v>
       </c>
     </row>
     <row r="87">
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="E87">
-        <v>2.738426690569612</v>
+        <v>2.736875954076597</v>
       </c>
     </row>
     <row r="88">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="E88">
-        <v>0.2722983512358803</v>
+        <v>0.2696962426671906</v>
       </c>
     </row>
     <row r="89">
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="E89">
-        <v>0.2424649704895659</v>
+        <v>0.2399418054292605</v>
       </c>
     </row>
     <row r="90">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="E92">
-        <v>7.919574726360763</v>
+        <v>7.913312964057985</v>
       </c>
     </row>
     <row r="93">
@@ -2494,7 +2494,7 @@
         </is>
       </c>
       <c r="E93">
-        <v>4.834827622609036</v>
+        <v>4.831050202099581</v>
       </c>
     </row>
     <row r="94">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="E94">
-        <v>7.693214392920564</v>
+        <v>7.686949815279053</v>
       </c>
     </row>
     <row r="95">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="E96">
-        <v>4.856728921661783</v>
+        <v>4.852774091618115</v>
       </c>
     </row>
     <row r="97">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="E97">
-        <v>2.957886999538077</v>
+        <v>2.955501240482398</v>
       </c>
     </row>
     <row r="98">
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="E98">
-        <v>0.3771131150114547</v>
+        <v>0.3731071042376444</v>
       </c>
     </row>
     <row r="99">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="E99">
-        <v>0.3307565431599546</v>
+        <v>0.3268747193307574</v>
       </c>
     </row>
     <row r="100">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="E102">
-        <v>8.867992909254859</v>
+        <v>8.858097427863067</v>
       </c>
     </row>
     <row r="103">
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="E103">
-        <v>5.187020968369822</v>
+        <v>5.181297431421172</v>
       </c>
     </row>
     <row r="104">
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="E104">
-        <v>8.615293115352285</v>
+        <v>8.605383861945073</v>
       </c>
     </row>
     <row r="105">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="E106">
-        <v>5.438837539797281</v>
+        <v>5.432581824675241</v>
       </c>
     </row>
     <row r="107">
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="E107">
-        <v>3.172828049373308</v>
+        <v>3.169209749745064</v>
       </c>
     </row>
     <row r="108">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="E108">
-        <v>0.5170375706142579</v>
+        <v>0.5109960524087945</v>
       </c>
     </row>
     <row r="109">
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="E109">
-        <v>0.447299167236678</v>
+        <v>0.4414514176306007</v>
       </c>
     </row>
     <row r="110">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="E112">
-        <v>9.314979763946461</v>
+        <v>9.300660305336137</v>
       </c>
     </row>
     <row r="113">
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="E113">
-        <v>5.389996733266686</v>
+        <v>5.381800690384947</v>
       </c>
     </row>
     <row r="114">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="E114">
-        <v>9.041882628318168</v>
+        <v>9.027545228090121</v>
       </c>
     </row>
     <row r="115">
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="E116">
-        <v>5.708143647684454</v>
+        <v>5.699092441934476</v>
       </c>
     </row>
     <row r="117">
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="E117">
-        <v>3.293955080251096</v>
+        <v>3.288774432541081</v>
       </c>
     </row>
     <row r="118">
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="E118">
-        <v>0.6980156822089248</v>
+        <v>0.689210280577324</v>
       </c>
     </row>
     <row r="119">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="E119">
-        <v>0.595929180730752</v>
+        <v>0.5874177533291117</v>
       </c>
     </row>
     <row r="120">
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="E122">
-        <v>9.756860481601358</v>
+        <v>9.736990398095871</v>
       </c>
     </row>
     <row r="123">
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="E123">
-        <v>5.585127539019714</v>
+        <v>5.573876182842909</v>
       </c>
     </row>
     <row r="124">
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="E124">
-        <v>9.458067353381958</v>
+        <v>9.438188748427601</v>
       </c>
     </row>
     <row r="125">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E126">
-        <v>5.97088120935064</v>
+        <v>5.958331839129924</v>
       </c>
     </row>
     <row r="127">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="E127">
-        <v>3.408433482748467</v>
+        <v>3.401327451507639</v>
       </c>
     </row>
     <row r="128">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E128">
-        <v>0.9190336191669054</v>
+        <v>0.9066227382903822</v>
       </c>
     </row>
     <row r="129">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="E129">
-        <v>0.7737481880294069</v>
+        <v>0.7617796330701907</v>
       </c>
     </row>
     <row r="130">
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="E132">
-        <v>10.20267210151867</v>
+        <v>10.17276557050015</v>
       </c>
     </row>
     <row r="133">
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="E133">
-        <v>5.778685346890076</v>
+        <v>5.761929229602338</v>
       </c>
     </row>
     <row r="134">
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="E134">
-        <v>9.876875893229242</v>
+        <v>9.846982978033253</v>
       </c>
     </row>
     <row r="135">
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="E135">
-        <v>5.578428071309288</v>
+        <v>5.561679582733794</v>
       </c>
     </row>
     <row r="136">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="E136">
-        <v>6.235275186202109</v>
+        <v>6.216403778443252</v>
       </c>
     </row>
     <row r="137">
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="E137">
-        <v>3.521663581385329</v>
+        <v>3.511090254723123</v>
       </c>
     </row>
     <row r="138">
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="E138">
-        <v>1.257519896459086</v>
+        <v>1.22177052589893</v>
       </c>
     </row>
     <row r="139">
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E139">
-        <v>1.051899863543003</v>
+        <v>1.017324756830415</v>
       </c>
     </row>
     <row r="140">
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="E142">
-        <v>10.66516651635904</v>
+        <v>10.6301694770379</v>
       </c>
     </row>
     <row r="143">
@@ -3644,7 +3644,7 @@
         </is>
       </c>
       <c r="E143">
-        <v>5.977635594978929</v>
+        <v>5.95824023147805</v>
       </c>
     </row>
     <row r="144">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="E144">
-        <v>10.30662892815394</v>
+        <v>10.27169843629056</v>
       </c>
     </row>
     <row r="145">
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="E145">
-        <v>5.760362142527002</v>
+        <v>5.741003659635411</v>
       </c>
     </row>
     <row r="146">
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="E146">
-        <v>6.506578426602037</v>
+        <v>6.484526794941174</v>
       </c>
     </row>
     <row r="147">
@@ -3736,7 +3736,7 @@
         </is>
       </c>
       <c r="E147">
-        <v>3.636518623814907</v>
+        <v>3.624297606833294</v>
       </c>
     </row>
     <row r="148">
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="E148">
-        <v>1.595256062469529</v>
+        <v>1.553599905396583</v>
       </c>
     </row>
     <row r="149">
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="E149">
-        <v>1.307397377968416</v>
+        <v>1.267141607169013</v>
       </c>
     </row>
     <row r="150">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="E152">
-        <v>11.14092868709874</v>
+        <v>11.10415493162242</v>
       </c>
     </row>
     <row r="153">
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="E153">
-        <v>6.181511539837332</v>
+        <v>6.161355143985892</v>
       </c>
     </row>
     <row r="154">
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="E154">
-        <v>10.756355490092</v>
+        <v>10.71965166052298</v>
       </c>
     </row>
     <row r="155">
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="E155">
-        <v>5.950965649963805</v>
+        <v>5.930847581834117</v>
       </c>
     </row>
     <row r="156">
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="E156">
-        <v>6.790490961551547</v>
+        <v>6.767319821180405</v>
       </c>
     </row>
     <row r="157">
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="E157">
-        <v>3.756846684344502</v>
+        <v>3.744146140937922</v>
       </c>
     </row>
     <row r="158">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="E158">
-        <v>1.978673343419327</v>
+        <v>1.935048669838099</v>
       </c>
     </row>
     <row r="159">
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="E159">
-        <v>1.581382739103087</v>
+        <v>1.539283704389651</v>
       </c>
     </row>
     <row r="160">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="E162">
-        <v>11.36056807776906</v>
+        <v>11.32643646512907</v>
       </c>
     </row>
     <row r="163">
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="E163">
-        <v>6.303469208793882</v>
+        <v>6.2847617378568</v>
       </c>
     </row>
     <row r="164">
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="E164">
-        <v>10.97152869115792</v>
+        <v>10.9374619803467</v>
       </c>
     </row>
     <row r="165">
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="E165">
-        <v>6.070253838645099</v>
+        <v>6.051581940274959</v>
       </c>
     </row>
     <row r="166">
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="E166">
-        <v>6.926329878213619</v>
+        <v>6.904823551831369</v>
       </c>
     </row>
     <row r="167">
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="E167">
-        <v>3.832153359342957</v>
+        <v>3.820365783408501</v>
       </c>
     </row>
     <row r="168">
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="E168">
-        <v>2.408614793740891</v>
+        <v>2.368052383723485</v>
       </c>
     </row>
     <row r="169">
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="E169">
-        <v>1.869445574125409</v>
+        <v>1.830400299100534</v>
       </c>
     </row>
     <row r="170">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="E172">
-        <v>11.69036045703421</v>
+        <v>11.66242612311274</v>
       </c>
     </row>
     <row r="173">
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="E173">
-        <v>6.484972953167466</v>
+        <v>6.469664649137417</v>
       </c>
     </row>
     <row r="174">
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="E174">
-        <v>11.29751296771964</v>
+        <v>11.26963175139844</v>
       </c>
     </row>
     <row r="175">
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="E175">
-        <v>6.249497212549938</v>
+        <v>6.234218017514459</v>
       </c>
     </row>
     <row r="176">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="E176">
-        <v>7.132123865372119</v>
+        <v>7.114522443812509</v>
       </c>
     </row>
     <row r="177">
@@ -4426,7 +4426,7 @@
         </is>
       </c>
       <c r="E177">
-        <v>3.945309763623195</v>
+        <v>3.935664002483767</v>
       </c>
     </row>
     <row r="178">
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="E178">
-        <v>2.88463224356534</v>
+        <v>2.851144035832656</v>
       </c>
     </row>
     <row r="179">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="E179">
-        <v>2.168420760785403</v>
+        <v>2.136324578035576</v>
       </c>
     </row>
     <row r="180">
@@ -4541,7 +4541,7 @@
         </is>
       </c>
       <c r="E182">
-        <v>12.02240953510418</v>
+        <v>12.00193034008529</v>
       </c>
     </row>
     <row r="183">
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="E183">
-        <v>6.667471755398739</v>
+        <v>6.656250632364094</v>
       </c>
     </row>
     <row r="184">
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="E184">
-        <v>11.62543574599301</v>
+        <v>11.60499549250385</v>
       </c>
     </row>
     <row r="185">
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="E185">
-        <v>6.429544753394109</v>
+        <v>6.418344967511432</v>
       </c>
     </row>
     <row r="186">
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="E186">
-        <v>7.339141629335326</v>
+        <v>7.326237690199269</v>
       </c>
     </row>
     <row r="187">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="E187">
-        <v>4.058973838771893</v>
+        <v>4.051903410049293</v>
       </c>
     </row>
     <row r="188">
@@ -4679,7 +4679,7 @@
         </is>
       </c>
       <c r="E188">
-        <v>3.413883523970914</v>
+        <v>3.388791374803855</v>
       </c>
     </row>
     <row r="189">
@@ -4702,7 +4702,7 @@
         </is>
       </c>
       <c r="E189">
-        <v>2.48350006683205</v>
+        <v>2.459639883782994</v>
       </c>
     </row>
     <row r="190">
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="E192">
-        <v>12.35032191270795</v>
+        <v>12.33630272301388</v>
       </c>
     </row>
     <row r="193">
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="E193">
-        <v>6.846920442835962</v>
+        <v>6.839239855187556</v>
       </c>
     </row>
     <row r="194">
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="E194">
-        <v>11.94947255222928</v>
+        <v>11.93548002025743</v>
       </c>
     </row>
     <row r="195">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="E195">
-        <v>6.606694203683279</v>
+        <v>6.599028220799953</v>
       </c>
     </row>
     <row r="196">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="E196">
-        <v>7.543706177800113</v>
+        <v>7.534872687500211</v>
       </c>
     </row>
     <row r="197">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="E197">
-        <v>4.170808348345372</v>
+        <v>4.165968810685187</v>
       </c>
     </row>
     <row r="198">
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="E198">
-        <v>3.993810085924701</v>
+        <v>3.975915642705499</v>
       </c>
     </row>
     <row r="199">
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="E199">
-        <v>2.813387508397184</v>
+        <v>2.796618879208717</v>
       </c>
     </row>
     <row r="200">
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="E202">
-        <v>12.65231611492216</v>
+        <v>12.6425709553002</v>
       </c>
     </row>
     <row r="203">
@@ -5024,7 +5024,7 @@
         </is>
       </c>
       <c r="E203">
-        <v>7.011271246341424</v>
+        <v>7.005931958095093</v>
       </c>
     </row>
     <row r="204">
@@ -5047,7 +5047,7 @@
         </is>
       </c>
       <c r="E204">
-        <v>12.24828455308924</v>
+        <v>12.23855792405029</v>
       </c>
     </row>
     <row r="205">
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="E205">
-        <v>6.769162275058484</v>
+        <v>6.763833139557505</v>
       </c>
     </row>
     <row r="206">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="E206">
-        <v>7.732346297858596</v>
+        <v>7.726205873563752</v>
       </c>
     </row>
     <row r="207">
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="E207">
-        <v>4.273374498304831</v>
+        <v>4.270010213209791</v>
       </c>
     </row>
     <row r="208">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="E208">
-        <v>4.621288997204061</v>
+        <v>4.608304639859295</v>
       </c>
     </row>
     <row r="209">
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="E209">
-        <v>3.155970887772704</v>
+        <v>3.144121242140184</v>
       </c>
     </row>
     <row r="210">
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="E212">
-        <v>12.934069023867</v>
+        <v>12.92637773326306</v>
       </c>
     </row>
     <row r="213">
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="E213">
-        <v>7.163828617194425</v>
+        <v>7.159613570168673</v>
       </c>
     </row>
     <row r="214">
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="E214">
-        <v>12.52704272214731</v>
+        <v>12.5193660566603</v>
       </c>
     </row>
     <row r="215">
@@ -5300,7 +5300,7 @@
         </is>
       </c>
       <c r="E215">
-        <v>6.919949033534879</v>
+        <v>6.91574200149111</v>
       </c>
     </row>
     <row r="216">
@@ -5323,7 +5323,7 @@
         </is>
       </c>
       <c r="E216">
-        <v>7.908326426926577</v>
+        <v>7.903480145334969</v>
       </c>
     </row>
     <row r="217">
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="E217">
-        <v>4.36856623136895</v>
+        <v>4.365910330576672</v>
       </c>
     </row>
     <row r="218">
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="E218">
-        <v>5.294975087582245</v>
+        <v>5.284812231933559</v>
       </c>
     </row>
     <row r="219">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="E219">
-        <v>3.509300063507389</v>
+        <v>3.500419041672183</v>
       </c>
     </row>
     <row r="220">
@@ -5461,7 +5461,7 @@
         </is>
       </c>
       <c r="E222">
-        <v>13.18835264322997</v>
+        <v>13.18092479410313</v>
       </c>
     </row>
     <row r="223">
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="E223">
-        <v>7.301066941846359</v>
+        <v>7.296996075513569</v>
       </c>
     </row>
     <row r="224">
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="E224">
-        <v>12.77795350525183</v>
+        <v>12.77053978030357</v>
       </c>
     </row>
     <row r="225">
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="E225">
-        <v>7.055186779170349</v>
+        <v>7.051123653657557</v>
       </c>
     </row>
     <row r="226">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="E226">
-        <v>8.066726491557805</v>
+        <v>8.062046204419756</v>
       </c>
     </row>
     <row r="227">
@@ -5576,7 +5576,7 @@
         </is>
       </c>
       <c r="E227">
-        <v>4.45394186721923</v>
+        <v>4.451376814670003</v>
       </c>
     </row>
     <row r="228">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="E228">
-        <v>5.996263367774328</v>
+        <v>5.987415292193649</v>
       </c>
     </row>
     <row r="229">
@@ -5622,7 +5622,7 @@
         </is>
       </c>
       <c r="E229">
-        <v>3.861025460058774</v>
+        <v>3.853775151335137</v>
       </c>
     </row>
     <row r="230">
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="E232">
-        <v>13.4282698596642</v>
+        <v>13.41979401175517</v>
       </c>
     </row>
     <row r="233">
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="E233">
-        <v>7.430984626992873</v>
+        <v>7.426338397169721</v>
       </c>
     </row>
     <row r="234">
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="E234">
-        <v>13.01236291409006</v>
+        <v>13.00390318314672</v>
       </c>
     </row>
     <row r="235">
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="E235">
-        <v>7.181815918574836</v>
+        <v>7.17717852363492</v>
       </c>
     </row>
     <row r="236">
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="E236">
-        <v>8.214709232876173</v>
+        <v>8.209368601789665</v>
       </c>
     </row>
     <row r="237">
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="E237">
-        <v>4.533882886962142</v>
+        <v>4.530955297923865</v>
       </c>
     </row>
     <row r="238">
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="E238">
-        <v>6.713804208111513</v>
+        <v>6.705223638020161</v>
       </c>
     </row>
     <row r="239">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="E239">
-        <v>4.20498224254898</v>
+        <v>4.198508566013609</v>
       </c>
     </row>
     <row r="240">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="E242">
-        <v>13.62670550446158</v>
+        <v>13.61609215741431</v>
       </c>
     </row>
     <row r="243">
@@ -5944,7 +5944,7 @@
         </is>
       </c>
       <c r="E243">
-        <v>7.537906262151327</v>
+        <v>7.532088310166611</v>
       </c>
     </row>
     <row r="244">
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="E244">
-        <v>13.20598586129463</v>
+        <v>13.19539269570318</v>
       </c>
     </row>
     <row r="245">
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="E245">
-        <v>7.285863760921702</v>
+        <v>7.280056871869392</v>
       </c>
     </row>
     <row r="246">
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="E246">
-        <v>8.336943466781209</v>
+        <v>8.330255997659421</v>
       </c>
     </row>
     <row r="247">
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="E247">
-        <v>4.599568326019653</v>
+        <v>4.595902434941511</v>
       </c>
     </row>
     <row r="248">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="E248">
-        <v>7.411433197489352</v>
+        <v>7.402265424610927</v>
       </c>
     </row>
     <row r="249">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="E249">
-        <v>4.530975953481016</v>
+        <v>4.524637424052766</v>
       </c>
     </row>
     <row r="250">
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="E252">
-        <v>13.80075854280086</v>
+        <v>13.78733204046965</v>
       </c>
     </row>
     <row r="253">
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="E253">
-        <v>7.632506036235054</v>
+        <v>7.625146818102116</v>
       </c>
     </row>
     <row r="254">
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="E254">
-        <v>13.37313249734105</v>
+        <v>13.35973152572719</v>
       </c>
     </row>
     <row r="255">
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="E255">
-        <v>7.376324664152661</v>
+        <v>7.36897943969533</v>
       </c>
     </row>
     <row r="256">
@@ -6243,7 +6243,7 @@
         </is>
       </c>
       <c r="E256">
-        <v>8.442463196244631</v>
+        <v>8.434003158204447</v>
       </c>
     </row>
     <row r="257">
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="E257">
-        <v>4.656676325688261</v>
+        <v>4.652039282933956</v>
       </c>
     </row>
     <row r="258">
@@ -6289,7 +6289,7 @@
         </is>
       </c>
       <c r="E258">
-        <v>8.076157374029657</v>
+        <v>8.065438199455658</v>
       </c>
     </row>
     <row r="259">
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="E259">
-        <v>4.836554376750088</v>
+        <v>4.829702908616006</v>
       </c>
     </row>
     <row r="260">
